--- a/index.xlsx
+++ b/index.xlsx
@@ -500,42 +500,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4131.98</v>
+        <v>3957.05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09</v>
+        <v>-1.24</v>
       </c>
       <c r="E2" t="n">
-        <v>4104.99</v>
+        <v>4032.26</v>
       </c>
       <c r="F2" t="n">
-        <v>4098.66</v>
+        <v>4073.9</v>
       </c>
       <c r="G2" t="n">
-        <v>4111.41</v>
+        <v>4100.79</v>
       </c>
       <c r="H2" t="n">
-        <v>19.54</v>
+        <v>-20.773</v>
       </c>
       <c r="I2" t="n">
-        <v>24.648</v>
+        <v>-2.47</v>
       </c>
       <c r="J2" t="n">
-        <v>5006852.78</v>
+        <v>6667983.87</v>
       </c>
       <c r="K2" t="n">
-        <v>6998939.76</v>
+        <v>7068821.86</v>
       </c>
       <c r="L2" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -550,42 +550,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14160.93</v>
+        <v>13866.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>14087.89</v>
+        <v>14060.57</v>
       </c>
       <c r="F3" t="n">
-        <v>14105.31</v>
+        <v>14184.55</v>
       </c>
       <c r="G3" t="n">
-        <v>14205.09</v>
+        <v>14218.97</v>
       </c>
       <c r="H3" t="n">
-        <v>74.718</v>
+        <v>-27.882</v>
       </c>
       <c r="I3" t="n">
-        <v>115.225</v>
+        <v>22.57</v>
       </c>
       <c r="J3" t="n">
-        <v>6819332.01</v>
+        <v>7329346.04</v>
       </c>
       <c r="K3" t="n">
-        <v>8455250.66</v>
+        <v>7663139.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -600,42 +600,42 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3284.74</v>
+        <v>3352.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.08</v>
+        <v>1.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3286.96</v>
+        <v>3328.93</v>
       </c>
       <c r="F4" t="n">
-        <v>3298.62</v>
+        <v>3313.67</v>
       </c>
       <c r="G4" t="n">
-        <v>3314.48</v>
+        <v>3292.26</v>
       </c>
       <c r="H4" t="n">
-        <v>8.856999999999999</v>
+        <v>10.891</v>
       </c>
       <c r="I4" t="n">
-        <v>17.198</v>
+        <v>3.179</v>
       </c>
       <c r="J4" t="n">
-        <v>2207151.23</v>
+        <v>2254016.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2549401.41</v>
+        <v>2303465.08</v>
       </c>
       <c r="L4" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -650,42 +650,42 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4713.82</v>
+        <v>4567.02</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="E5" t="n">
-        <v>4694.24</v>
+        <v>4623.52</v>
       </c>
       <c r="F5" t="n">
-        <v>4689.62</v>
+        <v>4646.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4705.64</v>
+        <v>4665.28</v>
       </c>
       <c r="H5" t="n">
-        <v>4.819</v>
+        <v>-21.085</v>
       </c>
       <c r="I5" t="n">
-        <v>7.236</v>
+        <v>-11.31</v>
       </c>
       <c r="J5" t="n">
-        <v>1733916.81</v>
+        <v>2578737.03</v>
       </c>
       <c r="K5" t="n">
-        <v>2805130.03</v>
+        <v>2742758.71</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/index.xlsx
+++ b/index.xlsx
@@ -500,42 +500,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3913.72</v>
+        <v>4023.42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.63</v>
+        <v>1.38</v>
       </c>
       <c r="E2" t="n">
-        <v>3885.84</v>
+        <v>3977.27</v>
       </c>
       <c r="F2" t="n">
-        <v>3959.05</v>
+        <v>3951.47</v>
       </c>
       <c r="G2" t="n">
-        <v>4039.44</v>
+        <v>3917.68</v>
       </c>
       <c r="H2" t="n">
-        <v>-56.067</v>
+        <v>20.254</v>
       </c>
       <c r="I2" t="n">
-        <v>-36.02</v>
+        <v>6.724</v>
       </c>
       <c r="J2" t="n">
-        <v>56134.3</v>
+        <v>59695.05</v>
       </c>
       <c r="K2" t="n">
-        <v>71815.03</v>
+        <v>51953.63</v>
       </c>
       <c r="L2" t="n">
-        <v>0.78</v>
+        <v>1.15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -550,42 +550,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13760.37</v>
+        <v>13828.63</v>
       </c>
       <c r="D3" t="n">
-        <v>1.13</v>
+        <v>2.24</v>
       </c>
       <c r="E3" t="n">
-        <v>13609.98</v>
+        <v>13619.74</v>
       </c>
       <c r="F3" t="n">
-        <v>13835.28</v>
+        <v>13495.85</v>
       </c>
       <c r="G3" t="n">
-        <v>14028.14</v>
+        <v>13337.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-138.459</v>
+        <v>141.321</v>
       </c>
       <c r="I3" t="n">
-        <v>-80.593</v>
+        <v>88.876</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.9</v>
+        <v>83096.48</v>
       </c>
       <c r="K3" t="n">
-        <v>76056.52</v>
+        <v>68550.50999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -600,42 +600,42 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3295.88</v>
+        <v>3294.55</v>
       </c>
       <c r="D4" t="n">
-        <v>0.71</v>
+        <v>2.85</v>
       </c>
       <c r="E4" t="n">
-        <v>3274.42</v>
+        <v>3241.42</v>
       </c>
       <c r="F4" t="n">
-        <v>3301.68</v>
+        <v>3219.53</v>
       </c>
       <c r="G4" t="n">
-        <v>3281.15</v>
+        <v>3188.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.292</v>
+        <v>37.745</v>
       </c>
       <c r="I4" t="n">
-        <v>0.843</v>
+        <v>28.973</v>
       </c>
       <c r="J4" t="n">
-        <v>17412.64</v>
+        <v>27193.28</v>
       </c>
       <c r="K4" t="n">
-        <v>22867.06</v>
+        <v>20334.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.76</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -650,42 +650,42 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4502.57</v>
+        <v>4717.75</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="E5" t="n">
-        <v>4482.06</v>
+        <v>4659.12</v>
       </c>
       <c r="F5" t="n">
-        <v>4552.79</v>
+        <v>4637.27</v>
       </c>
       <c r="G5" t="n">
-        <v>4608.73</v>
+        <v>4604.22</v>
       </c>
       <c r="H5" t="n">
-        <v>-51.968</v>
+        <v>24.115</v>
       </c>
       <c r="I5" t="n">
-        <v>-36.308</v>
+        <v>11.837</v>
       </c>
       <c r="J5" t="n">
-        <v>19240.04</v>
+        <v>23414.48</v>
       </c>
       <c r="K5" t="n">
-        <v>27748.57</v>
+        <v>17687.02</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/index.xlsx
+++ b/index.xlsx
@@ -500,42 +500,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4023.42</v>
+        <v>3892.44</v>
       </c>
       <c r="D2" t="n">
-        <v>1.38</v>
+        <v>-0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>3977.27</v>
+        <v>3901.67</v>
       </c>
       <c r="F2" t="n">
-        <v>3951.47</v>
+        <v>3939.81</v>
       </c>
       <c r="G2" t="n">
-        <v>3917.68</v>
+        <v>4024.93</v>
       </c>
       <c r="H2" t="n">
-        <v>20.254</v>
+        <v>-58.023</v>
       </c>
       <c r="I2" t="n">
-        <v>6.724</v>
+        <v>-40.652</v>
       </c>
       <c r="J2" t="n">
-        <v>59695.05</v>
+        <v>35094.1</v>
       </c>
       <c r="K2" t="n">
-        <v>51953.63</v>
+        <v>69261.84</v>
       </c>
       <c r="L2" t="n">
-        <v>1.15</v>
+        <v>0.51</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -550,42 +550,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13828.63</v>
+        <v>13603.87</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24</v>
+        <v>-1.14</v>
       </c>
       <c r="E3" t="n">
-        <v>13619.74</v>
+        <v>13661.65</v>
       </c>
       <c r="F3" t="n">
-        <v>13495.85</v>
+        <v>13764.9</v>
       </c>
       <c r="G3" t="n">
-        <v>13337.04</v>
+        <v>13985.04</v>
       </c>
       <c r="H3" t="n">
-        <v>141.321</v>
+        <v>-148.445</v>
       </c>
       <c r="I3" t="n">
-        <v>88.876</v>
+        <v>-94.72199999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>83096.48</v>
+        <v>38515.68</v>
       </c>
       <c r="K3" t="n">
-        <v>68550.50999999999</v>
+        <v>73313.33</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>0.53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -600,42 +600,42 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3294.55</v>
+        <v>3243.84</v>
       </c>
       <c r="D4" t="n">
-        <v>2.85</v>
+        <v>-1.58</v>
       </c>
       <c r="E4" t="n">
-        <v>3241.42</v>
+        <v>3276.15</v>
       </c>
       <c r="F4" t="n">
-        <v>3219.53</v>
+        <v>3290.36</v>
       </c>
       <c r="G4" t="n">
-        <v>3188.2</v>
+        <v>3278.64</v>
       </c>
       <c r="H4" t="n">
-        <v>37.745</v>
+        <v>-4.264</v>
       </c>
       <c r="I4" t="n">
-        <v>28.973</v>
+        <v>-0.299</v>
       </c>
       <c r="J4" t="n">
-        <v>27193.28</v>
+        <v>10123.14</v>
       </c>
       <c r="K4" t="n">
-        <v>20334.8</v>
+        <v>21966.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>0.46</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -650,42 +650,42 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4717.75</v>
+        <v>4460.62</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>-0.93</v>
       </c>
       <c r="E5" t="n">
-        <v>4659.12</v>
+        <v>4490.58</v>
       </c>
       <c r="F5" t="n">
-        <v>4637.27</v>
+        <v>4531.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4604.22</v>
+        <v>4595.33</v>
       </c>
       <c r="H5" t="n">
-        <v>24.115</v>
+        <v>-55.647</v>
       </c>
       <c r="I5" t="n">
-        <v>11.837</v>
+        <v>-40.281</v>
       </c>
       <c r="J5" t="n">
-        <v>23414.48</v>
+        <v>11630.48</v>
       </c>
       <c r="K5" t="n">
-        <v>17687.02</v>
+        <v>26583.79</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/index.xlsx
+++ b/index.xlsx
@@ -500,34 +500,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3892.44</v>
+        <v>3923.29</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.54</v>
+        <v>0.24</v>
       </c>
       <c r="E2" t="n">
-        <v>3901.67</v>
+        <v>3907.84</v>
       </c>
       <c r="F2" t="n">
-        <v>3939.81</v>
+        <v>3942.9</v>
       </c>
       <c r="G2" t="n">
-        <v>4024.93</v>
+        <v>4026.47</v>
       </c>
       <c r="H2" t="n">
-        <v>-58.023</v>
+        <v>-55.562</v>
       </c>
       <c r="I2" t="n">
-        <v>-40.652</v>
+        <v>-40.16</v>
       </c>
       <c r="J2" t="n">
-        <v>35094.1</v>
+        <v>59558.95</v>
       </c>
       <c r="K2" t="n">
-        <v>69261.84</v>
+        <v>70485.08</v>
       </c>
       <c r="L2" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -550,34 +550,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13603.87</v>
+        <v>13726.19</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.14</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>13661.65</v>
+        <v>13686.11</v>
       </c>
       <c r="F3" t="n">
-        <v>13764.9</v>
+        <v>13777.14</v>
       </c>
       <c r="G3" t="n">
-        <v>13985.04</v>
+        <v>13991.16</v>
       </c>
       <c r="H3" t="n">
-        <v>-148.445</v>
+        <v>-138.687</v>
       </c>
       <c r="I3" t="n">
-        <v>-94.72199999999999</v>
+        <v>-92.77</v>
       </c>
       <c r="J3" t="n">
-        <v>38515.68</v>
+        <v>65341.3</v>
       </c>
       <c r="K3" t="n">
-        <v>73313.33</v>
+        <v>74654.61</v>
       </c>
       <c r="L3" t="n">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -600,34 +600,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3243.84</v>
+        <v>3273.36</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.58</v>
+        <v>-0.68</v>
       </c>
       <c r="E4" t="n">
-        <v>3276.15</v>
+        <v>3282.05</v>
       </c>
       <c r="F4" t="n">
-        <v>3290.36</v>
+        <v>3293.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3278.64</v>
+        <v>3280.11</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.264</v>
+        <v>-1.909</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.299</v>
+        <v>0.172</v>
       </c>
       <c r="J4" t="n">
-        <v>10123.14</v>
+        <v>17720.84</v>
       </c>
       <c r="K4" t="n">
-        <v>21966.75</v>
+        <v>22346.63</v>
       </c>
       <c r="L4" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -650,34 +650,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4460.62</v>
+        <v>4491.95</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.93</v>
+        <v>-0.24</v>
       </c>
       <c r="E5" t="n">
-        <v>4490.58</v>
+        <v>4496.85</v>
       </c>
       <c r="F5" t="n">
-        <v>4531.7</v>
+        <v>4534.83</v>
       </c>
       <c r="G5" t="n">
-        <v>4595.33</v>
+        <v>4596.9</v>
       </c>
       <c r="H5" t="n">
-        <v>-55.647</v>
+        <v>-53.148</v>
       </c>
       <c r="I5" t="n">
-        <v>-40.281</v>
+        <v>-39.781</v>
       </c>
       <c r="J5" t="n">
-        <v>11630.48</v>
+        <v>20929.31</v>
       </c>
       <c r="K5" t="n">
-        <v>26583.79</v>
+        <v>27048.74</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>

--- a/index.xlsx
+++ b/index.xlsx
@@ -510,47 +510,47 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3891.86</v>
+        <v>3943.32</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8</v>
+        <v>1.32</v>
       </c>
       <c r="E2" t="n">
-        <v>3909.96</v>
+        <v>3912.25</v>
       </c>
       <c r="F2" t="n">
-        <v>3927.09</v>
+        <v>3915.13</v>
       </c>
       <c r="G2" t="n">
-        <v>4014.93</v>
+        <v>4007.97</v>
       </c>
       <c r="H2" t="n">
-        <v>-56.925</v>
+        <v>-53.221</v>
       </c>
       <c r="I2" t="n">
-        <v>-43.563</v>
+        <v>-45.514</v>
       </c>
       <c r="J2" t="n">
-        <v>60670.5</v>
+        <v>48120.76</v>
       </c>
       <c r="K2" t="n">
-        <v>68912.91</v>
+        <v>67493.10000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>3891.86</v>
+        <v>3929.92</v>
       </c>
       <c r="N2" t="n">
-        <v>3948.81</v>
+        <v>3955.94</v>
       </c>
       <c r="O2" t="n">
-        <v>3924.07</v>
+        <v>3939.57</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -566,47 +566,47 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13478.06</v>
+        <v>13685.37</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.81</v>
+        <v>1.54</v>
       </c>
       <c r="E3" t="n">
-        <v>13674.41</v>
+        <v>13651.29</v>
       </c>
       <c r="F3" t="n">
-        <v>13720.97</v>
+        <v>13670.73</v>
       </c>
       <c r="G3" t="n">
-        <v>13963.94</v>
+        <v>13952.32</v>
       </c>
       <c r="H3" t="n">
-        <v>-157.418</v>
+        <v>-152.502</v>
       </c>
       <c r="I3" t="n">
-        <v>-106.598</v>
+        <v>-114.951</v>
       </c>
       <c r="J3" t="n">
-        <v>66449.08</v>
+        <v>55829.34</v>
       </c>
       <c r="K3" t="n">
-        <v>73123.77</v>
+        <v>72212.91</v>
       </c>
       <c r="L3" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>13478.06</v>
+        <v>13603.79</v>
       </c>
       <c r="N3" t="n">
-        <v>13783.97</v>
+        <v>13740.97</v>
       </c>
       <c r="O3" t="n">
-        <v>13683.68</v>
+        <v>13731.39</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3184.95</v>
+        <v>3241.84</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.7</v>
+        <v>1.79</v>
       </c>
       <c r="E4" t="n">
-        <v>3268.73</v>
+        <v>3253.7</v>
       </c>
       <c r="F4" t="n">
-        <v>3283.8</v>
+        <v>3273.35</v>
       </c>
       <c r="G4" t="n">
-        <v>3278.89</v>
+        <v>3282.76</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.17</v>
+        <v>-11.742</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.953</v>
+        <v>-3.647</v>
       </c>
       <c r="J4" t="n">
-        <v>18574.09</v>
+        <v>15829.46</v>
       </c>
       <c r="K4" t="n">
-        <v>21803.79</v>
+        <v>21483.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="M4" t="n">
-        <v>3184.95</v>
+        <v>3206.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3280.48</v>
+        <v>3255.26</v>
       </c>
       <c r="O4" t="n">
-        <v>3247.28</v>
+        <v>3255.26</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4450.05</v>
+        <v>4521.95</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.93</v>
+        <v>1.62</v>
       </c>
       <c r="E5" t="n">
-        <v>4491.91</v>
+        <v>4488.81</v>
       </c>
       <c r="F5" t="n">
-        <v>4516.09</v>
+        <v>4502.45</v>
       </c>
       <c r="G5" t="n">
-        <v>4586.6</v>
+        <v>4582.57</v>
       </c>
       <c r="H5" t="n">
-        <v>-56.883</v>
+        <v>-53.128</v>
       </c>
       <c r="I5" t="n">
-        <v>-43.384</v>
+        <v>-45.111</v>
       </c>
       <c r="J5" t="n">
-        <v>22454.16</v>
+        <v>18381.45</v>
       </c>
       <c r="K5" t="n">
-        <v>26318.32</v>
+        <v>25722.22</v>
       </c>
       <c r="L5" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>4450.05</v>
+        <v>4492.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4523.17</v>
+        <v>4532.11</v>
       </c>
       <c r="O5" t="n">
-        <v>4491.92</v>
+        <v>4517.27</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -510,34 +510,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3943.32</v>
+        <v>3948.55</v>
       </c>
       <c r="D2" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="E2" t="n">
-        <v>3912.25</v>
+        <v>3913.3</v>
       </c>
       <c r="F2" t="n">
-        <v>3915.13</v>
+        <v>3915.65</v>
       </c>
       <c r="G2" t="n">
-        <v>4007.97</v>
+        <v>4008.23</v>
       </c>
       <c r="H2" t="n">
-        <v>-53.221</v>
+        <v>-52.804</v>
       </c>
       <c r="I2" t="n">
-        <v>-45.514</v>
+        <v>-45.431</v>
       </c>
       <c r="J2" t="n">
-        <v>48120.76</v>
+        <v>56461.16</v>
       </c>
       <c r="K2" t="n">
-        <v>67493.10000000001</v>
+        <v>67910.12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="M2" t="n">
         <v>3929.92</v>
@@ -566,34 +566,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13685.37</v>
+        <v>13706.52</v>
       </c>
       <c r="D3" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="E3" t="n">
-        <v>13651.29</v>
+        <v>13655.52</v>
       </c>
       <c r="F3" t="n">
-        <v>13670.73</v>
+        <v>13672.84</v>
       </c>
       <c r="G3" t="n">
-        <v>13952.32</v>
+        <v>13953.38</v>
       </c>
       <c r="H3" t="n">
-        <v>-152.502</v>
+        <v>-150.815</v>
       </c>
       <c r="I3" t="n">
-        <v>-114.951</v>
+        <v>-114.613</v>
       </c>
       <c r="J3" t="n">
-        <v>55829.34</v>
+        <v>65576.34</v>
       </c>
       <c r="K3" t="n">
-        <v>72212.91</v>
+        <v>72700.25999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="M3" t="n">
         <v>13603.79</v>
@@ -622,34 +622,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3241.84</v>
+        <v>3247.52</v>
       </c>
       <c r="D4" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="E4" t="n">
-        <v>3253.7</v>
+        <v>3254.84</v>
       </c>
       <c r="F4" t="n">
-        <v>3273.35</v>
+        <v>3273.91</v>
       </c>
       <c r="G4" t="n">
-        <v>3282.76</v>
+        <v>3283.04</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.742</v>
+        <v>-11.289</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.647</v>
+        <v>-3.557</v>
       </c>
       <c r="J4" t="n">
-        <v>15829.46</v>
+        <v>18679.91</v>
       </c>
       <c r="K4" t="n">
-        <v>21483.9</v>
+        <v>21626.42</v>
       </c>
       <c r="L4" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="M4" t="n">
         <v>3206.8</v>
@@ -678,34 +678,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4521.95</v>
+        <v>4526.07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="E5" t="n">
-        <v>4488.81</v>
+        <v>4489.63</v>
       </c>
       <c r="F5" t="n">
-        <v>4502.45</v>
+        <v>4502.86</v>
       </c>
       <c r="G5" t="n">
-        <v>4582.57</v>
+        <v>4582.78</v>
       </c>
       <c r="H5" t="n">
-        <v>-53.128</v>
+        <v>-52.799</v>
       </c>
       <c r="I5" t="n">
-        <v>-45.111</v>
+        <v>-45.045</v>
       </c>
       <c r="J5" t="n">
-        <v>18381.45</v>
+        <v>21648.32</v>
       </c>
       <c r="K5" t="n">
-        <v>25722.22</v>
+        <v>25885.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="M5" t="n">
         <v>4492.05</v>

--- a/index.xlsx
+++ b/index.xlsx
@@ -510,47 +510,47 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3948.55</v>
+        <v>3919.29</v>
       </c>
       <c r="D2" t="n">
-        <v>1.46</v>
+        <v>-0.74</v>
       </c>
       <c r="E2" t="n">
-        <v>3913.3</v>
+        <v>3919.34</v>
       </c>
       <c r="F2" t="n">
-        <v>3915.65</v>
+        <v>3906.92</v>
       </c>
       <c r="G2" t="n">
-        <v>4008.23</v>
+        <v>3998.77</v>
       </c>
       <c r="H2" t="n">
-        <v>-52.804</v>
+        <v>-51.293</v>
       </c>
       <c r="I2" t="n">
-        <v>-45.431</v>
+        <v>-46.601</v>
       </c>
       <c r="J2" t="n">
-        <v>56461.16</v>
+        <v>54421.28</v>
       </c>
       <c r="K2" t="n">
-        <v>67910.12</v>
+        <v>67182.45</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>3929.92</v>
+        <v>3900.12</v>
       </c>
       <c r="N2" t="n">
-        <v>3955.94</v>
+        <v>3952.58</v>
       </c>
       <c r="O2" t="n">
-        <v>3939.57</v>
+        <v>3940.8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -566,47 +566,47 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13706.52</v>
+        <v>13486.94</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="E3" t="n">
-        <v>13655.52</v>
+        <v>13631.62</v>
       </c>
       <c r="F3" t="n">
-        <v>13672.84</v>
+        <v>13631.38</v>
       </c>
       <c r="G3" t="n">
-        <v>13953.38</v>
+        <v>13923.29</v>
       </c>
       <c r="H3" t="n">
-        <v>-150.815</v>
+        <v>-162.653</v>
       </c>
       <c r="I3" t="n">
-        <v>-114.613</v>
+        <v>-125.052</v>
       </c>
       <c r="J3" t="n">
-        <v>65576.34</v>
+        <v>63603.87</v>
       </c>
       <c r="K3" t="n">
-        <v>72700.25999999999</v>
+        <v>72085.62</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>13603.79</v>
+        <v>13418.5</v>
       </c>
       <c r="N3" t="n">
-        <v>13740.97</v>
+        <v>13680.63</v>
       </c>
       <c r="O3" t="n">
-        <v>13731.39</v>
+        <v>13658.25</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3247.52</v>
+        <v>3172.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1.96</v>
+        <v>-2.31</v>
       </c>
       <c r="E4" t="n">
-        <v>3254.84</v>
+        <v>3234.87</v>
       </c>
       <c r="F4" t="n">
-        <v>3273.91</v>
+        <v>3260.27</v>
       </c>
       <c r="G4" t="n">
-        <v>3283.04</v>
+        <v>3280.83</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.289</v>
+        <v>-18.385</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.557</v>
+        <v>-6.774</v>
       </c>
       <c r="J4" t="n">
-        <v>18679.91</v>
+        <v>18044.89</v>
       </c>
       <c r="K4" t="n">
-        <v>21626.42</v>
+        <v>21295.49</v>
       </c>
       <c r="L4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3206.8</v>
+        <v>3155.13</v>
       </c>
       <c r="N4" t="n">
-        <v>3255.26</v>
+        <v>3229.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3255.26</v>
+        <v>3229.6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4526.07</v>
+        <v>4478.91</v>
       </c>
       <c r="D5" t="n">
-        <v>1.71</v>
+        <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>4489.63</v>
+        <v>4489.91</v>
       </c>
       <c r="F5" t="n">
-        <v>4502.86</v>
+        <v>4492.43</v>
       </c>
       <c r="G5" t="n">
-        <v>4582.78</v>
+        <v>4574.34</v>
       </c>
       <c r="H5" t="n">
-        <v>-52.799</v>
+        <v>-53.025</v>
       </c>
       <c r="I5" t="n">
-        <v>-45.045</v>
+        <v>-46.789</v>
       </c>
       <c r="J5" t="n">
-        <v>21648.32</v>
+        <v>19099.22</v>
       </c>
       <c r="K5" t="n">
-        <v>25885.56</v>
+        <v>25543.93</v>
       </c>
       <c r="L5" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>4492.05</v>
+        <v>4459.61</v>
       </c>
       <c r="N5" t="n">
-        <v>4532.11</v>
+        <v>4519.69</v>
       </c>
       <c r="O5" t="n">
-        <v>4517.27</v>
+        <v>4514.44</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -510,47 +510,47 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3880.1</v>
+        <v>3966.17</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>-0.72</v>
       </c>
       <c r="E2" t="n">
-        <v>3912.62</v>
+        <v>3930.14</v>
       </c>
       <c r="F2" t="n">
-        <v>3899.23</v>
+        <v>3921.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3986.56</v>
+        <v>3961.47</v>
       </c>
       <c r="H2" t="n">
-        <v>-52.688</v>
+        <v>-38.731</v>
       </c>
       <c r="I2" t="n">
-        <v>-47.865</v>
+        <v>-47.152</v>
       </c>
       <c r="J2" t="n">
-        <v>49269.91</v>
+        <v>54156.98</v>
       </c>
       <c r="K2" t="n">
-        <v>66412.12</v>
+        <v>63806.45</v>
       </c>
       <c r="L2" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3871.3</v>
+        <v>3955.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3929.53</v>
+        <v>3979.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3927.59</v>
+        <v>3967.63</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -566,47 +566,47 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13352.9</v>
+        <v>13996.27</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.99</v>
+        <v>-0.33</v>
       </c>
       <c r="E3" t="n">
-        <v>13550.12</v>
+        <v>13655.8</v>
       </c>
       <c r="F3" t="n">
-        <v>13580.05</v>
+        <v>13655.66</v>
       </c>
       <c r="G3" t="n">
-        <v>13882.3</v>
+        <v>13809.91</v>
       </c>
       <c r="H3" t="n">
-        <v>-179.433</v>
+        <v>-109.872</v>
       </c>
       <c r="I3" t="n">
-        <v>-134.948</v>
+        <v>-143.062</v>
       </c>
       <c r="J3" t="n">
-        <v>58657.22</v>
+        <v>65302.64</v>
       </c>
       <c r="K3" t="n">
-        <v>71372.09</v>
+        <v>69359.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>13345.61</v>
+        <v>13891.48</v>
       </c>
       <c r="N3" t="n">
-        <v>13558.91</v>
+        <v>14058.05</v>
       </c>
       <c r="O3" t="n">
-        <v>13553.65</v>
+        <v>13928.43</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3149.6</v>
+        <v>3323.3</v>
       </c>
       <c r="D4" t="n">
         <v>-0.73</v>
       </c>
       <c r="E4" t="n">
-        <v>3205.62</v>
+        <v>3230.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3240.02</v>
+        <v>3242.82</v>
       </c>
       <c r="G4" t="n">
-        <v>3276.84</v>
+        <v>3275.22</v>
       </c>
       <c r="H4" t="n">
-        <v>-25.015</v>
+        <v>-11.096</v>
       </c>
       <c r="I4" t="n">
-        <v>-9.929</v>
+        <v>-15.252</v>
       </c>
       <c r="J4" t="n">
-        <v>16815.42</v>
+        <v>20167.76</v>
       </c>
       <c r="K4" t="n">
-        <v>20999.03</v>
+        <v>20221.74</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3149.15</v>
+        <v>3301.65</v>
       </c>
       <c r="N4" t="n">
-        <v>3199.44</v>
+        <v>3340.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3197.77</v>
+        <v>3316.29</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4440.79</v>
+        <v>4566.22</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.85</v>
+        <v>-0.64</v>
       </c>
       <c r="E5" t="n">
-        <v>4477.55</v>
+        <v>4504.42</v>
       </c>
       <c r="F5" t="n">
-        <v>4479.81</v>
+        <v>4497.03</v>
       </c>
       <c r="G5" t="n">
-        <v>4563.35</v>
+        <v>4543.74</v>
       </c>
       <c r="H5" t="n">
-        <v>-55.331</v>
+        <v>-38.508</v>
       </c>
       <c r="I5" t="n">
-        <v>-48.233</v>
+        <v>-48.415</v>
       </c>
       <c r="J5" t="n">
-        <v>16832.17</v>
+        <v>18493.98</v>
       </c>
       <c r="K5" t="n">
-        <v>25192.9</v>
+        <v>23913.16</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>4437.6</v>
+        <v>4552.42</v>
       </c>
       <c r="N5" t="n">
-        <v>4494.46</v>
+        <v>4579.2</v>
       </c>
       <c r="O5" t="n">
-        <v>4492.85</v>
+        <v>4562.67</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -501,224 +501,224 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sz399006</t>
+          <t>sh000300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>创业板指</t>
+          <t>沪深300</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3667.79</v>
+        <v>4770.95</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.41</v>
+        <v>0.03</v>
       </c>
       <c r="E2" t="n">
-        <v>3701.46</v>
+        <v>4778.86</v>
       </c>
       <c r="F2" t="n">
-        <v>3636.18</v>
+        <v>4750.35</v>
       </c>
       <c r="G2" t="n">
-        <v>3448.31</v>
+        <v>4638.82</v>
       </c>
       <c r="H2" t="n">
-        <v>114.888</v>
+        <v>53.209</v>
       </c>
       <c r="I2" t="n">
-        <v>85.056</v>
+        <v>34.143</v>
       </c>
       <c r="J2" t="n">
-        <v>23383.9</v>
+        <v>19279.66</v>
       </c>
       <c r="K2" t="n">
-        <v>20133.61</v>
+        <v>20242.46</v>
       </c>
       <c r="L2" t="n">
-        <v>1.16</v>
+        <v>0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>3625</v>
+        <v>4762.64</v>
       </c>
       <c r="N2" t="n">
-        <v>3699.94</v>
+        <v>4795.17</v>
       </c>
       <c r="O2" t="n">
-        <v>3682.5</v>
+        <v>4776.34</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sh000300</t>
+          <t>sh000001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>沪深300</t>
+          <t>上证综指</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4769.37</v>
+        <v>4086.34</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.35</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>4776.15</v>
+        <v>4090.17</v>
       </c>
       <c r="F3" t="n">
-        <v>4737.87</v>
+        <v>4069.38</v>
       </c>
       <c r="G3" t="n">
-        <v>4625.4</v>
+        <v>4004.15</v>
       </c>
       <c r="H3" t="n">
-        <v>52.421</v>
+        <v>23.469</v>
       </c>
       <c r="I3" t="n">
-        <v>29.048</v>
+        <v>8.324</v>
       </c>
       <c r="J3" t="n">
-        <v>19379.83</v>
+        <v>58995.09</v>
       </c>
       <c r="K3" t="n">
-        <v>20240.48</v>
+        <v>57024.34</v>
       </c>
       <c r="L3" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="M3" t="n">
-        <v>4735.61</v>
+        <v>4071.08</v>
       </c>
       <c r="N3" t="n">
-        <v>4786.44</v>
+        <v>4092.83</v>
       </c>
       <c r="O3" t="n">
-        <v>4771.73</v>
+        <v>4074.81</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sz399001</t>
+          <t>sz399006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>深证成指</t>
+          <t>创业板指</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14940.3</v>
+        <v>3648.79</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="E4" t="n">
-        <v>15021.99</v>
+        <v>3695.71</v>
       </c>
       <c r="F4" t="n">
-        <v>14833.79</v>
+        <v>3653.42</v>
       </c>
       <c r="G4" t="n">
-        <v>14279.88</v>
+        <v>3465.96</v>
       </c>
       <c r="H4" t="n">
-        <v>295.412</v>
+        <v>110.455</v>
       </c>
       <c r="I4" t="n">
-        <v>194.711</v>
+        <v>89.878</v>
       </c>
       <c r="J4" t="n">
-        <v>70972.94</v>
+        <v>22238.33</v>
       </c>
       <c r="K4" t="n">
-        <v>67092.5</v>
+        <v>20374.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>14795.22</v>
+        <v>3640.11</v>
       </c>
       <c r="N4" t="n">
-        <v>15033.67</v>
+        <v>3686.94</v>
       </c>
       <c r="O4" t="n">
-        <v>14951.74</v>
+        <v>3677.89</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sh000001</t>
+          <t>sz399001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>上证综指</t>
+          <t>深证成指</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4079.9</v>
+        <v>14995.75</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>4089.32</v>
+        <v>15027.79</v>
       </c>
       <c r="F5" t="n">
-        <v>4059.6</v>
+        <v>14892.58</v>
       </c>
       <c r="G5" t="n">
-        <v>3995.52</v>
+        <v>14341.65</v>
       </c>
       <c r="H5" t="n">
-        <v>22.321</v>
+        <v>294.997</v>
       </c>
       <c r="I5" t="n">
-        <v>4.749</v>
+        <v>213.372</v>
       </c>
       <c r="J5" t="n">
-        <v>60503.18</v>
+        <v>70993</v>
       </c>
       <c r="K5" t="n">
-        <v>56881.3</v>
+        <v>67489.31</v>
       </c>
       <c r="L5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="M5" t="n">
-        <v>4061.15</v>
+        <v>14919.22</v>
       </c>
       <c r="N5" t="n">
-        <v>4092.61</v>
+        <v>15054.46</v>
       </c>
       <c r="O5" t="n">
-        <v>4081.03</v>
+        <v>14960.02</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -510,47 +510,47 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3677.15</v>
+        <v>3778.16</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.27</v>
+        <v>2.75</v>
       </c>
       <c r="E2" t="n">
-        <v>3655.52</v>
+        <v>3677.6</v>
       </c>
       <c r="F2" t="n">
-        <v>3679.54</v>
+        <v>3689.53</v>
       </c>
       <c r="G2" t="n">
-        <v>3528.72</v>
+        <v>3559</v>
       </c>
       <c r="H2" t="n">
-        <v>98.649</v>
+        <v>103.755</v>
       </c>
       <c r="I2" t="n">
-        <v>95.21599999999999</v>
+        <v>97.16</v>
       </c>
       <c r="J2" t="n">
-        <v>20798.18</v>
+        <v>25634.42</v>
       </c>
       <c r="K2" t="n">
-        <v>20891.32</v>
+        <v>21270.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>3660.22</v>
+        <v>3724.53</v>
       </c>
       <c r="N2" t="n">
-        <v>3718.4</v>
+        <v>3815.07</v>
       </c>
       <c r="O2" t="n">
-        <v>3704.11</v>
+        <v>3760.67</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -566,47 +566,47 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4807.31</v>
+        <v>4877.09</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>1.45</v>
       </c>
       <c r="E3" t="n">
-        <v>4783.24</v>
+        <v>4804.78</v>
       </c>
       <c r="F3" t="n">
-        <v>4775.63</v>
+        <v>4790.47</v>
       </c>
       <c r="G3" t="n">
-        <v>4684.21</v>
+        <v>4704.12</v>
       </c>
       <c r="H3" t="n">
-        <v>55.725</v>
+        <v>61.256</v>
       </c>
       <c r="I3" t="n">
-        <v>43.848</v>
+        <v>46.885</v>
       </c>
       <c r="J3" t="n">
-        <v>25063.34</v>
+        <v>27444.39</v>
       </c>
       <c r="K3" t="n">
-        <v>20494.15</v>
+        <v>20911.41</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>4797.54</v>
+        <v>4834.28</v>
       </c>
       <c r="N3" t="n">
-        <v>4829.27</v>
+        <v>4892.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4820.97</v>
+        <v>4857.65</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4112.16</v>
+        <v>4160.17</v>
       </c>
       <c r="D4" t="n">
-        <v>0.11</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>4092.91</v>
+        <v>4108.96</v>
       </c>
       <c r="F4" t="n">
-        <v>4088.27</v>
+        <v>4099.14</v>
       </c>
       <c r="G4" t="n">
-        <v>4030.88</v>
+        <v>4042.92</v>
       </c>
       <c r="H4" t="n">
-        <v>27.338</v>
+        <v>32.172</v>
       </c>
       <c r="I4" t="n">
-        <v>16.681</v>
+        <v>19.696</v>
       </c>
       <c r="J4" t="n">
-        <v>65691.27</v>
+        <v>70117.75</v>
       </c>
       <c r="K4" t="n">
-        <v>57548.02</v>
+        <v>58332.84</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>4100.97</v>
+        <v>4129.91</v>
       </c>
       <c r="N4" t="n">
-        <v>4118.76</v>
+        <v>4166.15</v>
       </c>
       <c r="O4" t="n">
-        <v>4107.3</v>
+        <v>4135.45</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15107.55</v>
+        <v>15459.62</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09</v>
+        <v>2.33</v>
       </c>
       <c r="E5" t="n">
-        <v>14999</v>
+        <v>15102.86</v>
       </c>
       <c r="F5" t="n">
-        <v>15005</v>
+        <v>15062.42</v>
       </c>
       <c r="G5" t="n">
-        <v>14549.06</v>
+        <v>14647.69</v>
       </c>
       <c r="H5" t="n">
-        <v>288.903</v>
+        <v>315.28</v>
       </c>
       <c r="I5" t="n">
-        <v>249.594</v>
+        <v>263.262</v>
       </c>
       <c r="J5" t="n">
-        <v>73770.37</v>
+        <v>82624.87</v>
       </c>
       <c r="K5" t="n">
-        <v>68610.03</v>
+        <v>69561.08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>15044.86</v>
+        <v>15254.99</v>
       </c>
       <c r="N5" t="n">
-        <v>15186.12</v>
+        <v>15534.67</v>
       </c>
       <c r="O5" t="n">
-        <v>15157.07</v>
+        <v>15323.19</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
